--- a/Corrected Airbrake Drag Coefficients.xlsx
+++ b/Corrected Airbrake Drag Coefficients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raaghav Batra\Documents\Projects\dragLookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1AFD97-F2C4-4BF8-A56B-5871BF02C6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54468CC7-818F-4703-9851-CD94934E4262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{39DDCD0F-584B-456C-86AF-10EEE41D7B4C}"/>
   </bookViews>
@@ -17,9 +17,6 @@
     <sheet name="Single Airbrake" sheetId="1" r:id="rId2"/>
     <sheet name="Rocket without Airbrakes" sheetId="2" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="247">
   <si>
     <t>WHAT CHANGED?</t>
   </si>
@@ -93,9 +90,6 @@
     <t>m2</t>
   </si>
   <si>
-    <t>Assuming the open rocket drag coefficient values use the same reference area, we can sum them together to get overall drag coeff.</t>
-  </si>
-  <si>
     <t>Total Drag coeff</t>
   </si>
   <si>
@@ -775,6 +769,39 @@
   </si>
   <si>
     <t>DP 195</t>
+  </si>
+  <si>
+    <t>THIS IS THE REFERENCE AREA USED IN THE OPENROCKET SIMULATION CONFIRMED</t>
+  </si>
+  <si>
+    <t>The open rocket drag coefficient values use the same reference area, we can sum them together to get overall drag coeff.</t>
+  </si>
+  <si>
+    <t>Run 1 Output Table</t>
+  </si>
+  <si>
+    <t>Flow Velocities (m/s)</t>
+  </si>
+  <si>
+    <t>Mass Flow Rate (kg/s)</t>
+  </si>
+  <si>
+    <t>Drag Coeffient</t>
+  </si>
+  <si>
+    <t>Run 2 Output Table</t>
+  </si>
+  <si>
+    <t>Run 3 Output Table</t>
+  </si>
+  <si>
+    <t>Run 4 Output Table</t>
+  </si>
+  <si>
+    <t>Run 5 Output Table</t>
+  </si>
+  <si>
+    <t>in mm</t>
   </si>
 </sst>
 </file>
@@ -821,7 +848,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -918,6 +945,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -959,7 +992,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -988,6 +1021,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1141,395 +1175,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Definitions"/>
-      <sheetName val="Area Calcs"/>
-      <sheetName val="MASS FLOW RATE AIRBRAKE"/>
-      <sheetName val="MASS FLOW RATE ROCKET"/>
-      <sheetName val="10%"/>
-      <sheetName val="RAW RESULT WRONG"/>
-      <sheetName val="NEW RAW RESULT"/>
-      <sheetName val="RESULT WRONG"/>
-      <sheetName val="RESULT CORRECT AIRBRAKE"/>
-      <sheetName val="RESULT ROCKET"/>
-      <sheetName val="Summary"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="L2">
-            <v>23.965099315068489</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="L3">
-            <v>21.682925880626218</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="L4">
-            <v>19.400752446183951</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="L5">
-            <v>17.11857901174168</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6">
-            <v>14.836405577299409</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="L7">
-            <v>12.554232142857144</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="L8">
-            <v>10.272058708414871</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="L9">
-            <v>7.9898852739726003</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="L10">
-            <v>5.707711839530333</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="L12">
-            <v>3.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="8">
-          <cell r="N8" t="str">
-            <v>Run 1 Output Table</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="N9" t="str">
-            <v>Flow Velocities (m/s)</v>
-          </cell>
-          <cell r="O9">
-            <v>55</v>
-          </cell>
-          <cell r="P9">
-            <v>63.333333333333336</v>
-          </cell>
-          <cell r="Q9">
-            <v>71.666666666666671</v>
-          </cell>
-          <cell r="R9">
-            <v>80</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="N10" t="str">
-            <v>Mass Flow Rate (kg/s)</v>
-          </cell>
-          <cell r="O10">
-            <v>0.93302176000000003</v>
-          </cell>
-          <cell r="P10">
-            <v>1.0743886933333333</v>
-          </cell>
-          <cell r="Q10">
-            <v>1.2157556266666667</v>
-          </cell>
-          <cell r="R10">
-            <v>1.3571225600000001</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="N11" t="str">
-            <v>Drag Coeffient</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="N13" t="str">
-            <v>Run 2 Output Table</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="N14" t="str">
-            <v>Flow Velocities (m/s)</v>
-          </cell>
-          <cell r="O14">
-            <v>45</v>
-          </cell>
-          <cell r="P14">
-            <v>51.666666666666664</v>
-          </cell>
-          <cell r="Q14">
-            <v>58.333333333333329</v>
-          </cell>
-          <cell r="R14">
-            <v>65</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="N15" t="str">
-            <v>Mass Flow Rate (kg/s)</v>
-          </cell>
-          <cell r="O15">
-            <v>0.75945996000000004</v>
-          </cell>
-          <cell r="P15">
-            <v>0.87197254666666657</v>
-          </cell>
-          <cell r="Q15">
-            <v>0.9844851333333331</v>
-          </cell>
-          <cell r="R15">
-            <v>1.0969977200000001</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="N16" t="str">
-            <v>Drag Coeffient</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="N18" t="str">
-            <v>Run 3 Output Table</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="N19" t="str">
-            <v>Flow Velocities (m/s)</v>
-          </cell>
-          <cell r="O19">
-            <v>35</v>
-          </cell>
-          <cell r="P19">
-            <v>39</v>
-          </cell>
-          <cell r="Q19">
-            <v>43</v>
-          </cell>
-          <cell r="R19">
-            <v>47</v>
-          </cell>
-          <cell r="S19">
-            <v>51</v>
-          </cell>
-          <cell r="T19">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="N20" t="str">
-            <v>Mass Flow Rate (kg/s)</v>
-          </cell>
-          <cell r="O20">
-            <v>0.58764103999999995</v>
-          </cell>
-          <cell r="P20">
-            <v>0.65480001599999993</v>
-          </cell>
-          <cell r="Q20">
-            <v>0.72195899200000002</v>
-          </cell>
-          <cell r="R20">
-            <v>0.78911796799999989</v>
-          </cell>
-          <cell r="S20">
-            <v>0.85627694399999998</v>
-          </cell>
-          <cell r="T20">
-            <v>0.92343591999999997</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="N21" t="str">
-            <v>Drag Coeffient</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="N23" t="str">
-            <v>Run 4 Output Table</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="N24" t="str">
-            <v>Flow Velocities (m/s)</v>
-          </cell>
-          <cell r="O24">
-            <v>15</v>
-          </cell>
-          <cell r="P24">
-            <v>19.285714285714285</v>
-          </cell>
-          <cell r="Q24">
-            <v>23.571428571428569</v>
-          </cell>
-          <cell r="R24">
-            <v>27.857142857142854</v>
-          </cell>
-          <cell r="S24">
-            <v>32.142857142857139</v>
-          </cell>
-          <cell r="T24">
-            <v>36.428571428571423</v>
-          </cell>
-          <cell r="U24">
-            <v>40.714285714285708</v>
-          </cell>
-          <cell r="V24">
-            <v>44.999999999999993</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="N25" t="str">
-            <v>Mass Flow Rate (kg/s)</v>
-          </cell>
-          <cell r="O25">
-            <v>0.25053900000000001</v>
-          </cell>
-          <cell r="P25">
-            <v>0.3221215714285714</v>
-          </cell>
-          <cell r="Q25">
-            <v>0.39370414285714284</v>
-          </cell>
-          <cell r="R25">
-            <v>0.46528671428571416</v>
-          </cell>
-          <cell r="S25">
-            <v>0.5368692857142856</v>
-          </cell>
-          <cell r="T25">
-            <v>0.60845185714285699</v>
-          </cell>
-          <cell r="U25">
-            <v>0.68003442857142848</v>
-          </cell>
-          <cell r="V25">
-            <v>0.75161699999999987</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="N26" t="str">
-            <v>Drag Coeffient</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="N28" t="str">
-            <v>Run 5 Output Table</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="N29" t="str">
-            <v>Flow Velocities (m/s)</v>
-          </cell>
-          <cell r="O29">
-            <v>0</v>
-          </cell>
-          <cell r="P29">
-            <v>2.2727272727272729</v>
-          </cell>
-          <cell r="Q29">
-            <v>4.5454545454545459</v>
-          </cell>
-          <cell r="R29">
-            <v>6.8181818181818183</v>
-          </cell>
-          <cell r="S29">
-            <v>9.0909090909090917</v>
-          </cell>
-          <cell r="T29">
-            <v>11.363636363636365</v>
-          </cell>
-          <cell r="U29">
-            <v>13.636363636363638</v>
-          </cell>
-          <cell r="V29">
-            <v>15.909090909090912</v>
-          </cell>
-          <cell r="W29">
-            <v>18.181818181818183</v>
-          </cell>
-          <cell r="X29">
-            <v>20.454545454545457</v>
-          </cell>
-          <cell r="Y29">
-            <v>22.72727272727273</v>
-          </cell>
-          <cell r="Z29">
-            <v>25.000000000000004</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="N30" t="str">
-            <v>Mass Flow Rate (kg/s)</v>
-          </cell>
-          <cell r="O30">
-            <v>0</v>
-          </cell>
-          <cell r="P30">
-            <v>3.7795409090909095E-2</v>
-          </cell>
-          <cell r="Q30">
-            <v>7.559081818181819E-2</v>
-          </cell>
-          <cell r="R30">
-            <v>0.11338622727272729</v>
-          </cell>
-          <cell r="S30">
-            <v>0.15118163636363638</v>
-          </cell>
-          <cell r="T30">
-            <v>0.18897704545454549</v>
-          </cell>
-          <cell r="U30">
-            <v>0.22677245454545461</v>
-          </cell>
-          <cell r="V30">
-            <v>0.2645678636363637</v>
-          </cell>
-          <cell r="W30">
-            <v>0.30236327272727276</v>
-          </cell>
-          <cell r="X30">
-            <v>0.34015868181818187</v>
-          </cell>
-          <cell r="Y30">
-            <v>0.37795409090909099</v>
-          </cell>
-          <cell r="Z30">
-            <v>0.41574950000000005</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="N31" t="str">
-            <v>Drag Coeffient</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1849,24 +1494,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <f>0.25*PI()*(83.8^2)</f>
         <v>5515.4114785687761</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <f>B3/(1000^2)</f>
@@ -1875,54 +1520,61 @@
       <c r="E3" t="s">
         <v>8</v>
       </c>
+      <c r="F3" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
       <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
         <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>35</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>36</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>37</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
       <c r="N4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>3.5999999999999999E-3</v>
@@ -1963,7 +1615,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>3.5999999999999999E-3</v>
@@ -2004,7 +1656,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>3.5999999999999999E-3</v>
@@ -2046,7 +1698,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>3.5999999999999999E-3</v>
@@ -2088,7 +1740,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>3.5999999999999999E-3</v>
@@ -2130,7 +1782,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>3.5999999999999999E-3</v>
@@ -2172,7 +1824,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>3.5999999999999999E-3</v>
@@ -2214,7 +1866,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>3.5999999999999999E-3</v>
@@ -2256,7 +1908,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>3.5999999999999999E-3</v>
@@ -2298,7 +1950,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>3.5999999999999999E-3</v>
@@ -2340,7 +1992,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>3.5999999999999999E-3</v>
@@ -2381,7 +2033,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>3.5999999999999999E-3</v>
@@ -2423,7 +2075,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>3.5999999999999999E-3</v>
@@ -2465,7 +2117,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>3.5999999999999999E-3</v>
@@ -2507,7 +2159,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>3.5999999999999999E-3</v>
@@ -2549,7 +2201,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>3.5999999999999999E-3</v>
@@ -2591,7 +2243,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>3.5999999999999999E-3</v>
@@ -2633,7 +2285,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>3.5999999999999999E-3</v>
@@ -2675,7 +2327,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>3.5999999999999999E-3</v>
@@ -2717,7 +2369,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>3.5999999999999999E-3</v>
@@ -2759,7 +2411,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>3.5999999999999999E-3</v>
@@ -2801,7 +2453,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>3.5999999999999999E-3</v>
@@ -2843,7 +2495,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>3.5999999999999999E-3</v>
@@ -2885,7 +2537,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28">
         <v>3.5999999999999999E-3</v>
@@ -2927,7 +2579,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29">
         <v>3.5999999999999999E-3</v>
@@ -2969,7 +2621,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30">
         <v>3.5999999999999999E-3</v>
@@ -3011,7 +2663,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31">
         <v>3.5999999999999999E-3</v>
@@ -3053,7 +2705,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32">
         <v>3.5999999999999999E-3</v>
@@ -3095,7 +2747,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B33">
         <v>3.5999999999999999E-3</v>
@@ -3137,7 +2789,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34">
         <v>3.5999999999999999E-3</v>
@@ -3179,7 +2831,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35">
         <v>3.5999999999999999E-3</v>
@@ -3221,7 +2873,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B36">
         <v>3.5999999999999999E-3</v>
@@ -3263,7 +2915,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B37">
         <v>3.5999999999999999E-3</v>
@@ -3305,7 +2957,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38">
         <v>5.7077120000000002E-3</v>
@@ -3347,7 +2999,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39">
         <v>5.7077120000000002E-3</v>
@@ -3389,7 +3041,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40">
         <v>5.7077120000000002E-3</v>
@@ -3430,7 +3082,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41">
         <v>5.7077120000000002E-3</v>
@@ -3471,7 +3123,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42">
         <v>5.7077120000000002E-3</v>
@@ -3512,7 +3164,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43">
         <v>5.7077120000000002E-3</v>
@@ -3553,7 +3205,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44">
         <v>5.7077120000000002E-3</v>
@@ -3594,7 +3246,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45">
         <v>5.7077120000000002E-3</v>
@@ -3635,7 +3287,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46">
         <v>5.7077120000000002E-3</v>
@@ -3676,7 +3328,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47">
         <v>5.7077120000000002E-3</v>
@@ -3717,7 +3369,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48">
         <v>5.7077120000000002E-3</v>
@@ -3758,7 +3410,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49">
         <v>5.7077120000000002E-3</v>
@@ -3799,7 +3451,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50">
         <v>5.7077120000000002E-3</v>
@@ -3840,7 +3492,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51">
         <v>5.7077120000000002E-3</v>
@@ -3881,7 +3533,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52">
         <v>5.7077120000000002E-3</v>
@@ -3922,7 +3574,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>5.7077120000000002E-3</v>
@@ -3963,7 +3615,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B54">
         <v>5.7077120000000002E-3</v>
@@ -4004,7 +3656,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55">
         <v>5.7077120000000002E-3</v>
@@ -4045,7 +3697,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56">
         <v>5.7077120000000002E-3</v>
@@ -4086,7 +3738,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57">
         <v>5.7077120000000002E-3</v>
@@ -4127,7 +3779,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58">
         <v>5.7077120000000002E-3</v>
@@ -4168,7 +3820,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59">
         <v>5.7077120000000002E-3</v>
@@ -4209,7 +3861,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60">
         <v>5.7077120000000002E-3</v>
@@ -4250,7 +3902,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61">
         <v>5.7077120000000002E-3</v>
@@ -4291,7 +3943,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62">
         <v>5.7077120000000002E-3</v>
@@ -4332,7 +3984,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63">
         <v>5.7077120000000002E-3</v>
@@ -4373,7 +4025,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64">
         <v>5.7077120000000002E-3</v>
@@ -4414,7 +4066,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65">
         <v>5.7077120000000002E-3</v>
@@ -4455,7 +4107,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66">
         <v>5.7077120000000002E-3</v>
@@ -4496,7 +4148,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67">
         <v>5.7077120000000002E-3</v>
@@ -4537,7 +4189,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B68">
         <v>5.7077120000000002E-3</v>
@@ -4578,7 +4230,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69">
         <v>5.7077120000000002E-3</v>
@@ -4619,7 +4271,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70">
         <v>5.7077120000000002E-3</v>
@@ -4660,7 +4312,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B71">
         <v>7.9898850000000004E-3</v>
@@ -4701,7 +4353,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B72">
         <v>7.9898850000000004E-3</v>
@@ -4742,7 +4394,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B73">
         <v>7.9898850000000004E-3</v>
@@ -4783,7 +4435,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74">
         <v>7.9898850000000004E-3</v>
@@ -4824,7 +4476,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75">
         <v>7.9898850000000004E-3</v>
@@ -4865,7 +4517,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76">
         <v>7.9898850000000004E-3</v>
@@ -4906,7 +4558,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77">
         <v>7.9898850000000004E-3</v>
@@ -4947,7 +4599,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78">
         <v>7.9898850000000004E-3</v>
@@ -4988,7 +4640,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79">
         <v>7.9898850000000004E-3</v>
@@ -5029,7 +4681,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80">
         <v>7.9898850000000004E-3</v>
@@ -5070,7 +4722,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81">
         <v>7.9898850000000004E-3</v>
@@ -5111,7 +4763,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B82">
         <v>7.9898850000000004E-3</v>
@@ -5152,7 +4804,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B83">
         <v>7.9898850000000004E-3</v>
@@ -5193,7 +4845,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B84">
         <v>7.9898850000000004E-3</v>
@@ -5234,7 +4886,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B85">
         <v>7.9898850000000004E-3</v>
@@ -5275,7 +4927,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B86">
         <v>7.9898850000000004E-3</v>
@@ -5316,7 +4968,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B87">
         <v>7.9898850000000004E-3</v>
@@ -5357,7 +5009,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B88">
         <v>7.9898850000000004E-3</v>
@@ -5398,7 +5050,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B89">
         <v>7.9898850000000004E-3</v>
@@ -5439,7 +5091,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B90">
         <v>7.9898850000000004E-3</v>
@@ -5480,7 +5132,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B91">
         <v>7.9898850000000004E-3</v>
@@ -5521,7 +5173,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B92">
         <v>7.9898850000000004E-3</v>
@@ -5562,7 +5214,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B93">
         <v>7.9898850000000004E-3</v>
@@ -5603,7 +5255,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94">
         <v>7.9898850000000004E-3</v>
@@ -5644,7 +5296,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B95">
         <v>7.9898850000000004E-3</v>
@@ -5685,7 +5337,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B96">
         <v>7.9898850000000004E-3</v>
@@ -5726,7 +5378,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B97">
         <v>7.9898850000000004E-3</v>
@@ -5767,7 +5419,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B98">
         <v>7.9898850000000004E-3</v>
@@ -5808,7 +5460,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B99">
         <v>7.9898850000000004E-3</v>
@@ -5849,7 +5501,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B100">
         <v>7.9898850000000004E-3</v>
@@ -5890,7 +5542,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B101">
         <v>7.9898850000000004E-3</v>
@@ -5931,7 +5583,7 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B102">
         <v>7.9898850000000004E-3</v>
@@ -5972,7 +5624,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B103">
         <v>7.9898850000000004E-3</v>
@@ -6013,7 +5665,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B104">
         <v>1.0272059E-2</v>
@@ -6054,7 +5706,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B105">
         <v>1.0272059E-2</v>
@@ -6095,7 +5747,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B106">
         <v>1.0272059E-2</v>
@@ -6136,7 +5788,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B107">
         <v>1.0272059E-2</v>
@@ -6177,7 +5829,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B108">
         <v>1.0272059E-2</v>
@@ -6218,7 +5870,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B109">
         <v>1.0272059E-2</v>
@@ -6259,7 +5911,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B110">
         <v>1.0272059E-2</v>
@@ -6300,7 +5952,7 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B111">
         <v>1.0272059E-2</v>
@@ -6341,7 +5993,7 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B112">
         <v>1.0272059E-2</v>
@@ -6382,7 +6034,7 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B113">
         <v>1.0272059E-2</v>
@@ -6423,7 +6075,7 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B114">
         <v>1.0272059E-2</v>
@@ -6464,7 +6116,7 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B115">
         <v>1.0272059E-2</v>
@@ -6505,7 +6157,7 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B116">
         <v>1.0272059E-2</v>
@@ -6546,7 +6198,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B117">
         <v>1.0272059E-2</v>
@@ -6587,7 +6239,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B118">
         <v>1.0272059E-2</v>
@@ -6628,7 +6280,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B119">
         <v>1.0272059E-2</v>
@@ -6669,7 +6321,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B120">
         <v>1.0272059E-2</v>
@@ -6710,7 +6362,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B121">
         <v>1.0272059E-2</v>
@@ -6751,7 +6403,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B122">
         <v>1.0272059E-2</v>
@@ -6792,7 +6444,7 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B123">
         <v>1.0272059E-2</v>
@@ -6833,7 +6485,7 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B124">
         <v>1.0272059E-2</v>
@@ -6874,7 +6526,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B125">
         <v>1.0272059E-2</v>
@@ -6915,7 +6567,7 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B126">
         <v>1.0272059E-2</v>
@@ -6956,7 +6608,7 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B127">
         <v>1.0272059E-2</v>
@@ -6997,7 +6649,7 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B128">
         <v>1.0272059E-2</v>
@@ -7038,7 +6690,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B129">
         <v>1.0272059E-2</v>
@@ -7079,7 +6731,7 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B130">
         <v>1.0272059E-2</v>
@@ -7120,7 +6772,7 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B131">
         <v>1.0272059E-2</v>
@@ -7161,7 +6813,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B132">
         <v>1.0272059E-2</v>
@@ -7202,7 +6854,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B133">
         <v>1.0272059E-2</v>
@@ -7243,7 +6895,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B134">
         <v>1.0272059E-2</v>
@@ -7284,7 +6936,7 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B135">
         <v>1.0272059E-2</v>
@@ -7325,7 +6977,7 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B136">
         <v>1.0272059E-2</v>
@@ -7366,7 +7018,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B137">
         <v>1.2554232E-2</v>
@@ -7407,7 +7059,7 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B138">
         <v>1.2554232E-2</v>
@@ -7448,7 +7100,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B139">
         <v>1.2554232E-2</v>
@@ -7489,7 +7141,7 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B140">
         <v>1.2554232E-2</v>
@@ -7530,7 +7182,7 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B141">
         <v>1.2554232E-2</v>
@@ -7571,7 +7223,7 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B142">
         <v>1.2554232E-2</v>
@@ -7612,7 +7264,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B143">
         <v>1.2554232E-2</v>
@@ -7653,7 +7305,7 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B144">
         <v>1.2554232E-2</v>
@@ -7694,7 +7346,7 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B145">
         <v>1.2554232E-2</v>
@@ -7735,7 +7387,7 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B146">
         <v>1.2554232E-2</v>
@@ -7776,7 +7428,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B147">
         <v>1.2554232E-2</v>
@@ -7817,7 +7469,7 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B148">
         <v>1.2554232E-2</v>
@@ -7858,7 +7510,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B149">
         <v>1.2554232E-2</v>
@@ -7899,7 +7551,7 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B150">
         <v>1.2554232E-2</v>
@@ -7940,7 +7592,7 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B151">
         <v>1.2554232E-2</v>
@@ -7981,7 +7633,7 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B152">
         <v>1.2554232E-2</v>
@@ -8022,7 +7674,7 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B153">
         <v>1.2554232E-2</v>
@@ -8063,7 +7715,7 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B154">
         <v>1.2554232E-2</v>
@@ -8104,7 +7756,7 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B155">
         <v>1.2554232E-2</v>
@@ -8145,7 +7797,7 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B156">
         <v>1.2554232E-2</v>
@@ -8186,7 +7838,7 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B157">
         <v>1.2554232E-2</v>
@@ -8227,7 +7879,7 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B158">
         <v>1.2554232E-2</v>
@@ -8268,7 +7920,7 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B159">
         <v>1.2554232E-2</v>
@@ -8309,7 +7961,7 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B160">
         <v>1.2554232E-2</v>
@@ -8350,7 +8002,7 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B161">
         <v>1.2554232E-2</v>
@@ -8391,7 +8043,7 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B162">
         <v>1.2554232E-2</v>
@@ -8432,7 +8084,7 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B163">
         <v>1.2554232E-2</v>
@@ -8473,7 +8125,7 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B164">
         <v>1.2554232E-2</v>
@@ -8514,7 +8166,7 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B165">
         <v>1.2554232E-2</v>
@@ -8555,7 +8207,7 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B166">
         <v>1.2554232E-2</v>
@@ -8596,7 +8248,7 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B167">
         <v>1.2554232E-2</v>
@@ -8637,7 +8289,7 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B168">
         <v>1.2554232E-2</v>
@@ -8678,7 +8330,7 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B169">
         <v>1.2554232E-2</v>
@@ -8719,7 +8371,7 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B170">
         <v>1.4836406E-2</v>
@@ -8760,7 +8412,7 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B171">
         <v>1.4836406E-2</v>
@@ -8801,7 +8453,7 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B172">
         <v>1.4836406E-2</v>
@@ -8842,7 +8494,7 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B173">
         <v>1.4836406E-2</v>
@@ -8883,7 +8535,7 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B174">
         <v>1.4836406E-2</v>
@@ -8924,7 +8576,7 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B175">
         <v>1.4836406E-2</v>
@@ -8965,7 +8617,7 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B176">
         <v>1.4836406E-2</v>
@@ -9006,7 +8658,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B177">
         <v>1.4836406E-2</v>
@@ -9047,7 +8699,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B178">
         <v>1.4836406E-2</v>
@@ -9088,7 +8740,7 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B179">
         <v>1.4836406E-2</v>
@@ -9129,7 +8781,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B180">
         <v>1.4836406E-2</v>
@@ -9170,7 +8822,7 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B181">
         <v>1.4836406E-2</v>
@@ -9211,7 +8863,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B182">
         <v>1.4836406E-2</v>
@@ -9252,7 +8904,7 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B183">
         <v>1.4836406E-2</v>
@@ -9293,7 +8945,7 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B184">
         <v>1.4836406E-2</v>
@@ -9334,7 +8986,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B185">
         <v>1.4836406E-2</v>
@@ -9375,7 +9027,7 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B186">
         <v>1.4836406E-2</v>
@@ -9416,7 +9068,7 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B187">
         <v>1.4836406E-2</v>
@@ -9457,7 +9109,7 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B188">
         <v>1.4836406E-2</v>
@@ -9498,7 +9150,7 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B189">
         <v>1.4836406E-2</v>
@@ -9539,7 +9191,7 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B190">
         <v>1.4836406E-2</v>
@@ -9580,7 +9232,7 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B191">
         <v>1.4836406E-2</v>
@@ -9621,7 +9273,7 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B192">
         <v>1.4836406E-2</v>
@@ -9662,7 +9314,7 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B193">
         <v>1.4836406E-2</v>
@@ -9703,7 +9355,7 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B194">
         <v>1.4836406E-2</v>
@@ -9744,7 +9396,7 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B195">
         <v>1.4836406E-2</v>
@@ -9785,7 +9437,7 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B196">
         <v>1.4836406E-2</v>
@@ -9826,7 +9478,7 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B197">
         <v>1.4836406E-2</v>
@@ -9867,7 +9519,7 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B198">
         <v>1.4836406E-2</v>
@@ -9908,7 +9560,7 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B199">
         <v>1.4836406E-2</v>
@@ -9949,7 +9601,7 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B200">
         <v>1.4836406E-2</v>
@@ -9990,7 +9642,7 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B201">
         <v>1.4836406E-2</v>
@@ -10031,7 +9683,7 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B202">
         <v>1.4836406E-2</v>
@@ -10072,7 +9724,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B203">
         <v>1.7118578999999998E-2</v>
@@ -10113,7 +9765,7 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B204">
         <v>1.7118578999999998E-2</v>
@@ -10154,7 +9806,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B205">
         <v>1.7118578999999998E-2</v>
@@ -10195,7 +9847,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B206">
         <v>1.7118578999999998E-2</v>
@@ -10236,7 +9888,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B207">
         <v>1.7118578999999998E-2</v>
@@ -10277,7 +9929,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B208">
         <v>1.7118578999999998E-2</v>
@@ -10318,7 +9970,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B209">
         <v>1.7118578999999998E-2</v>
@@ -10359,7 +10011,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B210">
         <v>1.7118578999999998E-2</v>
@@ -10400,7 +10052,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B211">
         <v>1.7118578999999998E-2</v>
@@ -10441,7 +10093,7 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B212">
         <v>1.7118578999999998E-2</v>
@@ -10482,7 +10134,7 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B213">
         <v>1.7118578999999998E-2</v>
@@ -10523,7 +10175,7 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B214">
         <v>1.7118578999999998E-2</v>
@@ -10564,7 +10216,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B215">
         <v>1.7118578999999998E-2</v>
@@ -10605,7 +10257,7 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B216">
         <v>1.7118578999999998E-2</v>
@@ -10646,7 +10298,7 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B217">
         <v>1.7118578999999998E-2</v>
@@ -10687,7 +10339,7 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B218">
         <v>1.7118578999999998E-2</v>
@@ -10728,7 +10380,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B219">
         <v>1.7118578999999998E-2</v>
@@ -10769,7 +10421,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B220">
         <v>1.7118578999999998E-2</v>
@@ -10810,7 +10462,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B221">
         <v>1.7118578999999998E-2</v>
@@ -10851,7 +10503,7 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B222">
         <v>1.7118578999999998E-2</v>
@@ -10892,7 +10544,7 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B223">
         <v>1.7118578999999998E-2</v>
@@ -10933,7 +10585,7 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B224">
         <v>1.7118578999999998E-2</v>
@@ -10974,7 +10626,7 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B225">
         <v>1.7118578999999998E-2</v>
@@ -11015,7 +10667,7 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B226">
         <v>1.7118578999999998E-2</v>
@@ -11056,7 +10708,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B227">
         <v>1.7118578999999998E-2</v>
@@ -11097,7 +10749,7 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B228">
         <v>1.7118578999999998E-2</v>
@@ -11138,7 +10790,7 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B229">
         <v>1.7118578999999998E-2</v>
@@ -11179,7 +10831,7 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B230">
         <v>1.7118578999999998E-2</v>
@@ -11220,7 +10872,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B231">
         <v>1.7118578999999998E-2</v>
@@ -11261,7 +10913,7 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B232">
         <v>1.7118578999999998E-2</v>
@@ -11302,7 +10954,7 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B233">
         <v>1.7118578999999998E-2</v>
@@ -11343,7 +10995,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B234">
         <v>1.7118578999999998E-2</v>
@@ -11384,7 +11036,7 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B235">
         <v>1.7118578999999998E-2</v>
@@ -11425,7 +11077,7 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B236">
         <v>1.9400752E-2</v>
@@ -11466,7 +11118,7 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B237">
         <v>1.9400752E-2</v>
@@ -11507,7 +11159,7 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B238">
         <v>1.9400752E-2</v>
@@ -11548,7 +11200,7 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B239">
         <v>1.9400752E-2</v>
@@ -11589,7 +11241,7 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B240">
         <v>1.9400752E-2</v>
@@ -11630,7 +11282,7 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B241">
         <v>1.9400752E-2</v>
@@ -11671,7 +11323,7 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B242">
         <v>1.9400752E-2</v>
@@ -11712,7 +11364,7 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B243">
         <v>1.9400752E-2</v>
@@ -11753,7 +11405,7 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B244">
         <v>1.9400752E-2</v>
@@ -11794,7 +11446,7 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B245">
         <v>1.9400752E-2</v>
@@ -11835,7 +11487,7 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B246">
         <v>1.9400752E-2</v>
@@ -11876,7 +11528,7 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B247">
         <v>1.9400752E-2</v>
@@ -11917,7 +11569,7 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B248">
         <v>1.9400752E-2</v>
@@ -11958,7 +11610,7 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B249">
         <v>1.9400752E-2</v>
@@ -11999,7 +11651,7 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B250">
         <v>1.9400752E-2</v>
@@ -12040,7 +11692,7 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B251">
         <v>1.9400752E-2</v>
@@ -12081,7 +11733,7 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B252">
         <v>1.9400752E-2</v>
@@ -12122,7 +11774,7 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B253">
         <v>1.9400752E-2</v>
@@ -12163,7 +11815,7 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B254">
         <v>1.9400752E-2</v>
@@ -12204,7 +11856,7 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B255">
         <v>1.9400752E-2</v>
@@ -12245,7 +11897,7 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B256">
         <v>1.9400752E-2</v>
@@ -12286,7 +11938,7 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B257">
         <v>1.9400752E-2</v>
@@ -12327,7 +11979,7 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B258">
         <v>1.9400752E-2</v>
@@ -12368,7 +12020,7 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B259">
         <v>1.9400752E-2</v>
@@ -12409,7 +12061,7 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B260">
         <v>1.9400752E-2</v>
@@ -12450,7 +12102,7 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B261">
         <v>1.9400752E-2</v>
@@ -12491,7 +12143,7 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B262">
         <v>1.9400752E-2</v>
@@ -12532,7 +12184,7 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B263">
         <v>1.9400752E-2</v>
@@ -12573,7 +12225,7 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B264">
         <v>1.9400752E-2</v>
@@ -12614,7 +12266,7 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B265">
         <v>1.9400752E-2</v>
@@ -12655,7 +12307,7 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B266">
         <v>1.9400752E-2</v>
@@ -12696,7 +12348,7 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B267">
         <v>1.9400752E-2</v>
@@ -12737,7 +12389,7 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B268">
         <v>1.9400752E-2</v>
@@ -12778,7 +12430,7 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B269">
         <v>2.1682926000000002E-2</v>
@@ -12819,7 +12471,7 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B270">
         <v>2.1682926000000002E-2</v>
@@ -12860,7 +12512,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B271">
         <v>2.1682926000000002E-2</v>
@@ -12901,7 +12553,7 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B272">
         <v>2.1682926000000002E-2</v>
@@ -12942,7 +12594,7 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B273">
         <v>2.1682926000000002E-2</v>
@@ -12983,7 +12635,7 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B274">
         <v>2.1682926000000002E-2</v>
@@ -13024,7 +12676,7 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B275">
         <v>2.1682926000000002E-2</v>
@@ -13065,7 +12717,7 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B276">
         <v>2.1682926000000002E-2</v>
@@ -13106,7 +12758,7 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B277">
         <v>2.1682926000000002E-2</v>
@@ -13147,7 +12799,7 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B278">
         <v>2.1682926000000002E-2</v>
@@ -13188,7 +12840,7 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B279">
         <v>2.1682926000000002E-2</v>
@@ -13229,7 +12881,7 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B280">
         <v>2.1682926000000002E-2</v>
@@ -13270,7 +12922,7 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B281">
         <v>2.1682926000000002E-2</v>
@@ -13311,7 +12963,7 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B282">
         <v>2.1682926000000002E-2</v>
@@ -13352,7 +13004,7 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B283">
         <v>2.1682926000000002E-2</v>
@@ -13393,7 +13045,7 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B284">
         <v>2.1682926000000002E-2</v>
@@ -13434,7 +13086,7 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B285">
         <v>2.1682926000000002E-2</v>
@@ -13475,7 +13127,7 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B286">
         <v>2.1682926000000002E-2</v>
@@ -13516,7 +13168,7 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B287">
         <v>2.1682926000000002E-2</v>
@@ -13557,7 +13209,7 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B288">
         <v>2.1682926000000002E-2</v>
@@ -13598,7 +13250,7 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B289">
         <v>2.1682926000000002E-2</v>
@@ -13639,7 +13291,7 @@
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B290">
         <v>2.1682926000000002E-2</v>
@@ -13680,7 +13332,7 @@
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B291">
         <v>2.1682926000000002E-2</v>
@@ -13721,7 +13373,7 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B292">
         <v>2.1682926000000002E-2</v>
@@ -13762,7 +13414,7 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B293">
         <v>2.1682926000000002E-2</v>
@@ -13803,7 +13455,7 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B294">
         <v>2.1682926000000002E-2</v>
@@ -13844,7 +13496,7 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B295">
         <v>2.1682926000000002E-2</v>
@@ -13885,7 +13537,7 @@
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B296">
         <v>2.1682926000000002E-2</v>
@@ -13926,7 +13578,7 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B297">
         <v>2.1682926000000002E-2</v>
@@ -13967,7 +13619,7 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B298">
         <v>2.1682926000000002E-2</v>
@@ -14008,7 +13660,7 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B299">
         <v>2.1682926000000002E-2</v>
@@ -14049,7 +13701,7 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B300">
         <v>2.1682926000000002E-2</v>
@@ -14090,7 +13742,7 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B301">
         <v>2.1682926000000002E-2</v>
@@ -14131,7 +13783,7 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B302">
         <v>2.3965099E-2</v>
@@ -14172,7 +13824,7 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B303">
         <v>2.3965099E-2</v>
@@ -14213,7 +13865,7 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B304">
         <v>2.3965099E-2</v>
@@ -14254,7 +13906,7 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B305">
         <v>2.3965099E-2</v>
@@ -14295,7 +13947,7 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B306">
         <v>2.3965099E-2</v>
@@ -14336,7 +13988,7 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B307">
         <v>2.3965099E-2</v>
@@ -14377,7 +14029,7 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B308">
         <v>2.3965099E-2</v>
@@ -14418,7 +14070,7 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B309">
         <v>2.3965099E-2</v>
@@ -14459,7 +14111,7 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B310">
         <v>2.3965099E-2</v>
@@ -14500,7 +14152,7 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B311">
         <v>2.3965099E-2</v>
@@ -14541,7 +14193,7 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B312">
         <v>2.3965099E-2</v>
@@ -14582,7 +14234,7 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B313">
         <v>2.3965099E-2</v>
@@ -14623,7 +14275,7 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B314">
         <v>2.3965099E-2</v>
@@ -14664,7 +14316,7 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B315">
         <v>2.3965099E-2</v>
@@ -14705,7 +14357,7 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B316">
         <v>2.3965099E-2</v>
@@ -14746,7 +14398,7 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B317">
         <v>2.3965099E-2</v>
@@ -14787,7 +14439,7 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B318">
         <v>2.3965099E-2</v>
@@ -14828,7 +14480,7 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B319">
         <v>2.3965099E-2</v>
@@ -14869,7 +14521,7 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B320">
         <v>2.3965099E-2</v>
@@ -14910,7 +14562,7 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B321">
         <v>2.3965099E-2</v>
@@ -14951,7 +14603,7 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B322">
         <v>2.3965099E-2</v>
@@ -14992,7 +14644,7 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B323">
         <v>2.3965099E-2</v>
@@ -15033,7 +14685,7 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B324">
         <v>2.3965099E-2</v>
@@ -15074,7 +14726,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B325">
         <v>2.3965099E-2</v>
@@ -15115,7 +14767,7 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B326">
         <v>2.3965099E-2</v>
@@ -15156,7 +14808,7 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B327">
         <v>2.3965099E-2</v>
@@ -15197,7 +14849,7 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B328">
         <v>2.3965099E-2</v>
@@ -15238,7 +14890,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B329">
         <v>2.3965099E-2</v>
@@ -15279,7 +14931,7 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B330">
         <v>2.3965099E-2</v>
@@ -15320,7 +14972,7 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B331">
         <v>2.3965099E-2</v>
@@ -15361,7 +15013,7 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B332">
         <v>2.3965099E-2</v>
@@ -15402,7 +15054,7 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B333">
         <v>2.3965099E-2</v>
@@ -15443,7 +15095,7 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B334">
         <v>2.3965099E-2</v>
@@ -15495,6 +15147,7 @@
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="27" width="12" bestFit="1" customWidth="1"/>
@@ -15504,20 +15157,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -15526,19 +15179,19 @@
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="Q2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -15628,7 +15281,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>237</v>
       </c>
       <c r="Q5" s="6">
         <v>63.333333333333336</v>
@@ -15666,10 +15319,10 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
       <c r="Q6" s="6">
         <v>71.666666666666671</v>
@@ -15742,19 +15395,19 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="P9" s="7"/>
-      <c r="Q9" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
+      <c r="Q9" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="P10" s="8">
@@ -15937,19 +15590,19 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="P16" s="7"/>
-      <c r="Q16" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
+      <c r="Q16" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
+      <c r="AA16" s="30"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="P17" s="9">
@@ -16201,52 +15854,58 @@
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N8</f>
-        <v>Run 1 Output Table</v>
+      <c r="A25" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="K25" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" t="s">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="29"/>
-      <c r="X25" s="29"/>
-      <c r="Y25" s="29"/>
-      <c r="Z25" s="29"/>
-      <c r="AA25" s="29"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+      <c r="AA25" s="30"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A26" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N9</f>
-        <v>Flow Velocities (m/s)</v>
+      <c r="A26" t="s">
+        <v>239</v>
       </c>
       <c r="B26">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O9</f>
         <v>55</v>
       </c>
       <c r="C26">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P9</f>
         <v>63.333333333333336</v>
       </c>
       <c r="D26">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q9</f>
         <v>71.666666666666671</v>
       </c>
       <c r="E26">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R9</f>
         <v>80</v>
       </c>
       <c r="K26">
-        <f>'[1]Area Calcs'!L12</f>
         <v>3.6</v>
+      </c>
+      <c r="L26">
+        <f>K26/1000</f>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="M26">
+        <v>10</v>
       </c>
       <c r="P26" s="11">
         <v>1.1499999999999999</v>
@@ -16286,29 +15945,30 @@
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A27" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N10</f>
-        <v>Mass Flow Rate (kg/s)</v>
+      <c r="A27" t="s">
+        <v>240</v>
       </c>
       <c r="B27" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O10</f>
         <v>0.93302176000000003</v>
       </c>
       <c r="C27" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P10</f>
         <v>1.0743886933333333</v>
       </c>
       <c r="D27" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q10</f>
         <v>1.2157556266666667</v>
       </c>
       <c r="E27" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R10</f>
         <v>1.3571225600000001</v>
       </c>
       <c r="K27">
-        <f>'[1]Area Calcs'!L10</f>
         <v>5.707711839530333</v>
+      </c>
+      <c r="L27">
+        <f t="shared" ref="L27:L35" si="0">K27/1000</f>
+        <v>5.7077118395303331E-3</v>
+      </c>
+      <c r="M27">
+        <v>20</v>
       </c>
       <c r="Q27" s="6" cm="1">
         <f t="array" ref="Q27:Q34">TRANSPOSE(B41:I41)</f>
@@ -16346,17 +16006,22 @@
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A28" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N11</f>
-        <v>Drag Coeffient</v>
+      <c r="A28" t="s">
+        <v>241</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="K28">
-        <f>'[1]Area Calcs'!L9</f>
         <v>7.9898852739726003</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="0"/>
+        <v>7.9898852739726002E-3</v>
+      </c>
+      <c r="M28">
+        <v>30</v>
       </c>
       <c r="Q28" s="6">
         <v>19.285714285714285</v>
@@ -16394,8 +16059,14 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K29">
-        <f>'[1]Area Calcs'!L8</f>
         <v>10.272058708414871</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="0"/>
+        <v>1.0272058708414871E-2</v>
+      </c>
+      <c r="M29">
+        <v>40</v>
       </c>
       <c r="Q29" s="6">
         <v>23.571428571428569</v>
@@ -16432,13 +16103,18 @@
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N13</f>
-        <v>Run 2 Output Table</v>
+      <c r="A30" s="10" t="s">
+        <v>242</v>
       </c>
       <c r="K30">
-        <f>'[1]Area Calcs'!L7</f>
         <v>12.554232142857144</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="0"/>
+        <v>1.2554232142857143E-2</v>
+      </c>
+      <c r="M30">
+        <v>50</v>
       </c>
       <c r="Q30" s="6">
         <v>27.857142857142854</v>
@@ -16475,29 +16151,30 @@
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A31" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N14</f>
-        <v>Flow Velocities (m/s)</v>
+      <c r="A31" t="s">
+        <v>239</v>
       </c>
       <c r="B31">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O14</f>
         <v>45</v>
       </c>
       <c r="C31">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P14</f>
         <v>51.666666666666664</v>
       </c>
       <c r="D31">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q14</f>
         <v>58.333333333333329</v>
       </c>
       <c r="E31">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R14</f>
         <v>65</v>
       </c>
       <c r="K31">
-        <f>'[1]Area Calcs'!L6</f>
         <v>14.836405577299409</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="0"/>
+        <v>1.483640557729941E-2</v>
+      </c>
+      <c r="M31">
+        <v>60</v>
       </c>
       <c r="Q31" s="6">
         <v>32.142857142857139</v>
@@ -16534,29 +16211,30 @@
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A32" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N15</f>
-        <v>Mass Flow Rate (kg/s)</v>
+      <c r="A32" t="s">
+        <v>240</v>
       </c>
       <c r="B32" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O15</f>
         <v>0.75945996000000004</v>
       </c>
       <c r="C32" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P15</f>
         <v>0.87197254666666657</v>
       </c>
       <c r="D32" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q15</f>
         <v>0.9844851333333331</v>
       </c>
       <c r="E32" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R15</f>
         <v>1.0969977200000001</v>
       </c>
       <c r="K32">
-        <f>'[1]Area Calcs'!L5</f>
         <v>17.11857901174168</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="0"/>
+        <v>1.7118579011741679E-2</v>
+      </c>
+      <c r="M32">
+        <v>70</v>
       </c>
       <c r="Q32" s="6">
         <v>36.428571428571423</v>
@@ -16593,17 +16271,22 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N16</f>
-        <v>Drag Coeffient</v>
+      <c r="A33" t="s">
+        <v>241</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="K33">
-        <f>'[1]Area Calcs'!L4</f>
         <v>19.400752446183951</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="0"/>
+        <v>1.9400752446183951E-2</v>
+      </c>
+      <c r="M33">
+        <v>80</v>
       </c>
       <c r="Q33" s="6">
         <v>40.714285714285708</v>
@@ -16641,8 +16324,14 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K34">
-        <f>'[1]Area Calcs'!L3</f>
         <v>21.682925880626218</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="0"/>
+        <v>2.1682925880626217E-2</v>
+      </c>
+      <c r="M34">
+        <v>90</v>
       </c>
       <c r="Q34" s="6">
         <v>44.999999999999993</v>
@@ -16679,47 +16368,45 @@
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N18</f>
-        <v>Run 3 Output Table</v>
+      <c r="A35" s="10" t="s">
+        <v>243</v>
       </c>
       <c r="K35">
-        <f>'[1]Area Calcs'!L2</f>
         <v>23.965099315068489</v>
       </c>
+      <c r="L35">
+        <f t="shared" si="0"/>
+        <v>2.3965099315068489E-2</v>
+      </c>
+      <c r="M35">
+        <v>100</v>
+      </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N19</f>
-        <v>Flow Velocities (m/s)</v>
+      <c r="A36" t="s">
+        <v>239</v>
       </c>
       <c r="B36">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O19</f>
         <v>35</v>
       </c>
       <c r="C36">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P19</f>
         <v>39</v>
       </c>
       <c r="D36">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q19</f>
         <v>43</v>
       </c>
       <c r="E36">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R19</f>
         <v>47</v>
       </c>
       <c r="F36">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!S19</f>
         <v>51</v>
       </c>
       <c r="G36">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!T19</f>
         <v>55</v>
       </c>
       <c r="P36" s="7"/>
       <c r="Q36" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R36" s="14"/>
       <c r="S36" s="14"/>
@@ -16733,32 +16420,25 @@
       <c r="AA36" s="14"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N20</f>
-        <v>Mass Flow Rate (kg/s)</v>
+      <c r="A37" t="s">
+        <v>240</v>
       </c>
       <c r="B37" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O20</f>
         <v>0.58764103999999995</v>
       </c>
       <c r="C37" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P20</f>
         <v>0.65480001599999993</v>
       </c>
       <c r="D37" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q20</f>
         <v>0.72195899200000002</v>
       </c>
       <c r="E37" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R20</f>
         <v>0.78911796799999989</v>
       </c>
       <c r="F37" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!S20</f>
         <v>0.85627694399999998</v>
       </c>
       <c r="G37" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!T20</f>
         <v>0.92343591999999997</v>
       </c>
       <c r="P37" s="15">
@@ -16799,9 +16479,8 @@
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N21</f>
-        <v>Drag Coeffient</v>
+      <c r="A38" t="s">
+        <v>241</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -16880,9 +16559,8 @@
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N23</f>
-        <v>Run 4 Output Table</v>
+      <c r="A40" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="Q40" s="6">
         <v>4.5454545454545459</v>
@@ -16919,40 +16597,31 @@
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A41" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N24</f>
-        <v>Flow Velocities (m/s)</v>
+      <c r="A41" t="s">
+        <v>239</v>
       </c>
       <c r="B41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O24</f>
         <v>15</v>
       </c>
       <c r="C41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P24</f>
         <v>19.285714285714285</v>
       </c>
       <c r="D41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q24</f>
         <v>23.571428571428569</v>
       </c>
       <c r="E41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R24</f>
         <v>27.857142857142854</v>
       </c>
       <c r="F41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!S24</f>
         <v>32.142857142857139</v>
       </c>
       <c r="G41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!T24</f>
         <v>36.428571428571423</v>
       </c>
       <c r="H41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!U24</f>
         <v>40.714285714285708</v>
       </c>
       <c r="I41">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!V24</f>
         <v>44.999999999999993</v>
       </c>
       <c r="Q41" s="6">
@@ -16990,40 +16659,31 @@
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N25</f>
-        <v>Mass Flow Rate (kg/s)</v>
+      <c r="A42" t="s">
+        <v>240</v>
       </c>
       <c r="B42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O25</f>
         <v>0.25053900000000001</v>
       </c>
       <c r="C42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P25</f>
         <v>0.3221215714285714</v>
       </c>
       <c r="D42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q25</f>
         <v>0.39370414285714284</v>
       </c>
       <c r="E42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R25</f>
         <v>0.46528671428571416</v>
       </c>
       <c r="F42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!S25</f>
         <v>0.5368692857142856</v>
       </c>
       <c r="G42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!T25</f>
         <v>0.60845185714285699</v>
       </c>
       <c r="H42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!U25</f>
         <v>0.68003442857142848</v>
       </c>
       <c r="I42" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!V25</f>
         <v>0.75161699999999987</v>
       </c>
       <c r="Q42" s="6">
@@ -17061,9 +16721,8 @@
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N26</f>
-        <v>Drag Coeffient</v>
+      <c r="A43" t="s">
+        <v>241</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -17143,9 +16802,8 @@
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A45" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N28</f>
-        <v>Run 5 Output Table</v>
+      <c r="A45" t="s">
+        <v>245</v>
       </c>
       <c r="Q45" s="6">
         <v>15.909090909090912</v>
@@ -17182,56 +16840,43 @@
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A46" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N29</f>
-        <v>Flow Velocities (m/s)</v>
+      <c r="A46" t="s">
+        <v>239</v>
       </c>
       <c r="B46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O29</f>
         <v>0</v>
       </c>
       <c r="C46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P29</f>
         <v>2.2727272727272729</v>
       </c>
       <c r="D46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q29</f>
         <v>4.5454545454545459</v>
       </c>
       <c r="E46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R29</f>
         <v>6.8181818181818183</v>
       </c>
       <c r="F46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!S29</f>
         <v>9.0909090909090917</v>
       </c>
       <c r="G46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!T29</f>
         <v>11.363636363636365</v>
       </c>
       <c r="H46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!U29</f>
         <v>13.636363636363638</v>
       </c>
       <c r="I46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!V29</f>
         <v>15.909090909090912</v>
       </c>
       <c r="J46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!W29</f>
         <v>18.181818181818183</v>
       </c>
       <c r="K46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!X29</f>
         <v>20.454545454545457</v>
       </c>
       <c r="L46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Y29</f>
         <v>22.72727272727273</v>
       </c>
       <c r="M46">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Z29</f>
         <v>25.000000000000004</v>
       </c>
       <c r="Q46" s="6">
@@ -17269,56 +16914,43 @@
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A47" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N30</f>
-        <v>Mass Flow Rate (kg/s)</v>
+      <c r="A47" t="s">
+        <v>240</v>
       </c>
       <c r="B47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!O30</f>
         <v>0</v>
       </c>
       <c r="C47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!P30</f>
         <v>3.7795409090909095E-2</v>
       </c>
       <c r="D47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Q30</f>
         <v>7.559081818181819E-2</v>
       </c>
       <c r="E47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!R30</f>
         <v>0.11338622727272729</v>
       </c>
       <c r="F47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!S30</f>
         <v>0.15118163636363638</v>
       </c>
       <c r="G47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!T30</f>
         <v>0.18897704545454549</v>
       </c>
       <c r="H47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!U30</f>
         <v>0.22677245454545461</v>
       </c>
       <c r="I47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!V30</f>
         <v>0.2645678636363637</v>
       </c>
       <c r="J47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!W30</f>
         <v>0.30236327272727276</v>
       </c>
       <c r="K47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!X30</f>
         <v>0.34015868181818187</v>
       </c>
       <c r="L47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Y30</f>
         <v>0.37795409090909099</v>
       </c>
       <c r="M47" s="12">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!Z30</f>
         <v>0.41574950000000005</v>
       </c>
       <c r="Q47" s="6">
@@ -17356,9 +16988,8 @@
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A48" t="str">
-        <f>'[1]MASS FLOW RATE AIRBRAKE'!N31</f>
-        <v>Drag Coeffient</v>
+      <c r="A48" t="s">
+        <v>241</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -17508,7 +17139,7 @@
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G54">
-        <f t="shared" ref="G54:G63" si="0">K26/1000</f>
+        <f t="shared" ref="G54:G63" si="1">K26/1000</f>
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="H54">
@@ -17520,7 +17151,7 @@
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.7077118395303331E-3</v>
       </c>
       <c r="H55">
@@ -17532,7 +17163,7 @@
     </row>
     <row r="56" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.9898852739726002E-3</v>
       </c>
       <c r="H56">
@@ -17544,7 +17175,7 @@
     </row>
     <row r="57" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0272058708414871E-2</v>
       </c>
       <c r="H57">
@@ -17556,7 +17187,7 @@
     </row>
     <row r="58" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2554232142857143E-2</v>
       </c>
       <c r="H58">
@@ -17568,7 +17199,7 @@
     </row>
     <row r="59" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.483640557729941E-2</v>
       </c>
       <c r="H59">
@@ -17580,7 +17211,7 @@
     </row>
     <row r="60" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.7118579011741679E-2</v>
       </c>
       <c r="H60">
@@ -17592,7 +17223,7 @@
     </row>
     <row r="61" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.9400752446183951E-2</v>
       </c>
       <c r="H61">
@@ -17604,7 +17235,7 @@
     </row>
     <row r="62" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.1682925880626217E-2</v>
       </c>
       <c r="H62">
@@ -17616,7 +17247,7 @@
     </row>
     <row r="63" spans="2:27" x14ac:dyDescent="0.25">
       <c r="G63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.3965099315068489E-2</v>
       </c>
       <c r="H63">
@@ -17652,16 +17283,16 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>19</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -17679,7 +17310,7 @@
         <v>0.66300000000000003</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -17700,7 +17331,7 @@
         <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
